--- a/public/downloads/goldfin-owner-command-center-sample.xlsx
+++ b/public/downloads/goldfin-owner-command-center-sample.xlsx
@@ -18,8 +18,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="$#,##0;[Red]($#,##0);-"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot; mo&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
   <fonts count="6">
@@ -189,7 +189,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -212,7 +212,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="8">
@@ -222,7 +222,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="9">
@@ -232,7 +232,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <v>-41180</v>
+        <v>-71900</v>
       </c>
     </row>
     <row r="10">
@@ -242,7 +242,7 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="11">
@@ -313,7 +313,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 to 2026-05-31</t>
+          <t>2026-05-01 to 2026-05-31</t>
         </is>
       </c>
     </row>
@@ -344,7 +344,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="7">
@@ -354,7 +354,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="8">
@@ -364,7 +364,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>-41180</v>
+        <v>-71900</v>
       </c>
     </row>
     <row r="9">
@@ -374,7 +374,7 @@
         </is>
       </c>
       <c r="B9" s="9">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="10">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <v>6800</v>
+        <v>72948</v>
       </c>
     </row>
     <row r="11">
@@ -394,7 +394,7 @@
         </is>
       </c>
       <c r="B11" s="11">
-        <v>5.6</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="12">
@@ -588,7 +588,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B4" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="5">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="6">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>41180</v>
+        <v>71900</v>
       </c>
     </row>
     <row r="7">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="8">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>6800</v>
+        <v>72948</v>
       </c>
     </row>
     <row r="9">
@@ -660,8 +660,8 @@
           <t>runwayMonths</t>
         </is>
       </c>
-      <c r="B9" s="8">
-        <v>5.6</v>
+      <c r="B9" s="11">
+        <v>3.67</v>
       </c>
     </row>
     <row r="10">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <v>14600</v>
+        <v>22700</v>
       </c>
     </row>
     <row r="11">
@@ -680,7 +680,7 @@
           <t>revenueVsPriorPct</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="10">
         <v>6.4</v>
       </c>
     </row>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="13">
@@ -700,7 +700,7 @@
           <t>profitVsPriorPct</t>
         </is>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="10">
         <v>3.1</v>
       </c>
     </row>
@@ -720,7 +720,7 @@
           <t>coveragePct</t>
         </is>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="10">
         <v>94</v>
       </c>
     </row>
@@ -730,7 +730,7 @@
           <t>transactionsCount</t>
         </is>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="12">
         <v>118</v>
       </c>
     </row>
@@ -740,7 +740,7 @@
           <t>reserve_floor_months</t>
         </is>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="12">
         <v>3</v>
       </c>
     </row>
@@ -758,7 +758,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Detail</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
@@ -770,12 +770,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Not embedded</t>
+          <t>Transaction detail</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>The current frontend report snapshot does not include raw transaction rows. Server-side XLSX generation can populate this sheet from the transactions table.</t>
+          <t>This planning workbook summarizes your connected bank and card activity. Line-item transaction detail lives in your GoldFin Desk account and your own bank export.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/goldfin-owner-command-center-sample.xlsx
+++ b/public/downloads/goldfin-owner-command-center-sample.xlsx
@@ -217,7 +217,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Sample figures</t>
+          <t>Sample figures (pre-filled - type over them)</t>
         </is>
       </c>
     </row>
@@ -251,16 +251,36 @@
         <v>71900</v>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Profit this month</t>
+        </is>
+      </c>
+      <c r="B14" s="8">
+        <v>24500</v>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Profit margin</t>
+        </is>
+      </c>
+      <c r="B15" s="10">
+        <v>25.41</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Prefer it filled from your bank every month? That is GoldFin Reports - goldfindesk.com/pricing</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>A planning artifact, not tax, accounting, credit, legal, or investment advice.</t>
         </is>
@@ -274,7 +294,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,62 +370,108 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>Owner pay you took (this month)</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t>Reserve months target</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B11" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Results</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Net cash</t>
-        </is>
-      </c>
-      <c r="B13" s="9">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Where you stand</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="str">
+        <f>IF(($B$8-$B$9)&lt;0,"You spent more than you earned this month - act now",IF($B$7&lt;$B$9*$B$11,"Below your cash reserve - build cash before new spending",IF($B$8=0,"No income yet - enter your numbers",IF(($B$8-$B$9)/$B$8&lt;0.1,"Thin profit margin - review pricing or costs","Healthy - profitable and above your reserve"))))</f>
+        <v>Healthy - profitable and above your reserve</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>The numbers that matter</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Profit this month (net cash)</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
         <f>$B$8-$B$9</f>
         <v>24500</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Cash coverage (months, if income paused)</t>
-        </is>
-      </c>
-      <c r="B14" s="11">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Profit margin</t>
+        </is>
+      </c>
+      <c r="B18" s="10">
+        <f>IF($B$8=0,0,($B$8-$B$9)/$B$8*100)</f>
+        <v>25.41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Owner pay as % of income</t>
+        </is>
+      </c>
+      <c r="B19" s="10">
+        <f>IF($B$8=0,0,$B$10/$B$8*100)</f>
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Cash coverage (months at this burn)</t>
+        </is>
+      </c>
+      <c r="B20" s="11">
         <f>IF($B$9=0,0,$B$7/$B$9)</f>
         <v>3.73</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Reserve floor target</t>
         </is>
       </c>
-      <c r="B15" s="8">
-        <f>$B$9*$B$10</f>
+      <c r="B21" s="8">
+        <f>$B$9*$B$11</f>
         <v>215700</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Cash over / (under) reserve</t>
         </is>
       </c>
-      <c r="B16" s="9">
-        <f>$B$7-$B$9*$B$10</f>
+      <c r="B22" s="9">
+        <f>$B$7-$B$9*$B$11</f>
         <v>52300</v>
       </c>
     </row>
